--- a/ZAKAT MAAL_INFAQ_SHODAQOH 2026.xlsx
+++ b/ZAKAT MAAL_INFAQ_SHODAQOH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP Laptop\OneDrive\Desktop\IRMADA\FORM_ZAKAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB6AA07-4D39-464A-A515-AC7EB579EDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5418A02E-A3C3-4523-8AFF-1D4090DFDF4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -180,7 +180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -313,11 +313,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -348,6 +359,37 @@
     <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="42" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -372,51 +414,437 @@
     <xf numFmtId="42" fontId="8" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD0E0E3"/>
+          <bgColor rgb="FFD0E0E3"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -427,6 +855,25 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{205762B1-0D0E-45FB-916F-BE339F4E51EC}" name="Table4" displayName="Table4" ref="A5:J207" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="12">
+  <autoFilter ref="A5:J207" xr:uid="{205762B1-0D0E-45FB-916F-BE339F4E51EC}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{DC51E9D7-0A17-4647-9420-F3970DB5883C}" name="No" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{E3C87204-3A2B-4A44-8039-41FFC8C84FD1}" name="Tanggal" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{F66F8B55-8E74-4AE4-A5E7-57B77095AA17}" name="Jam" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{DF48F774-EE7D-4583-BD7F-A20F82986E7C}" name="Nama" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{E31F6EC0-A342-4257-84B2-7A88D48D6A94}" name="Alamat" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{D2406624-608E-495E-AC02-D87D64710057}" name="RT" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{C1BFE869-DE46-4081-80C1-971DB3205274}" name="RW" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{DFEC0D5D-41BD-422B-8A5B-80C0DD156E44}" name="KATEGORI" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{966766F5-3A30-4278-87F9-04E1A8988203}" name="Jenis Zakat" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{F900385D-C4CA-48A8-9852-4DA218AE26CE}" name="NOMINAL" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -627,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:S1003"/>
@@ -635,6 +1082,9 @@
   <cols>
     <col min="1" max="1" width="6.28515625" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
     <col min="12" max="12" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -644,82 +1094,82 @@
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" spans="1:19" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:19" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+    <row r="5" spans="1:19" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G5" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="30" t="s">
+      <c r="I5" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="40" t="s">
+      <c r="J5" s="39" t="s">
         <v>16</v>
       </c>
       <c r="K5" s="7"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="29"/>
-    </row>
-    <row r="6" spans="1:19" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="31"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="16"/>
+    </row>
+    <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
       <c r="F6" s="41"/>
       <c r="G6" s="41"/>
       <c r="H6" s="41"/>
-      <c r="I6" s="31"/>
+      <c r="I6" s="40"/>
       <c r="J6" s="41"/>
       <c r="K6" s="8"/>
       <c r="L6" s="9"/>
@@ -728,15 +1178,15 @@
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="44"/>
       <c r="K7" s="10"/>
       <c r="L7" s="11"/>
     </row>
@@ -767,14 +1217,14 @@
       <c r="J9" s="5"/>
       <c r="K9" s="10"/>
       <c r="L9" s="11"/>
-      <c r="N9" s="32" t="s">
+      <c r="N9" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33"/>
-      <c r="S9" s="34"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="25"/>
     </row>
     <row r="10" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
@@ -789,12 +1239,12 @@
       <c r="J10" s="5"/>
       <c r="K10" s="10"/>
       <c r="L10" s="11"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
-      <c r="S10" s="37"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="28"/>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
@@ -809,17 +1259,17 @@
       <c r="J11" s="5"/>
       <c r="K11" s="10"/>
       <c r="L11" s="11"/>
-      <c r="N11" s="20" t="s">
+      <c r="N11" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="O11" s="22">
-        <f>SUMIF(H7:H206, "perorangan", J7:J206)</f>
+      <c r="O11" s="17">
+        <f>SUMIF(H6:H206, "perorangan", J6:J206)</f>
         <v>0</v>
       </c>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="24"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="19"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3"/>
@@ -834,12 +1284,12 @@
       <c r="J12" s="5"/>
       <c r="K12" s="10"/>
       <c r="L12" s="11"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="26"/>
-      <c r="S12" s="27"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="22"/>
     </row>
     <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3"/>
@@ -854,17 +1304,17 @@
       <c r="J13" s="5"/>
       <c r="K13" s="10"/>
       <c r="L13" s="11"/>
-      <c r="N13" s="20" t="s">
+      <c r="N13" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="O13" s="22">
-        <f>SUMIF(H7:H206, "instansi", J7:J206)</f>
+      <c r="O13" s="17">
+        <f>SUMIF(H6:H206, "instansi", J6:J206)</f>
         <v>0</v>
       </c>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="24"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="19"/>
     </row>
     <row r="14" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
@@ -879,12 +1329,12 @@
       <c r="J14" s="5"/>
       <c r="K14" s="10"/>
       <c r="L14" s="11"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="26"/>
-      <c r="S14" s="27"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="22"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
@@ -899,17 +1349,17 @@
       <c r="J15" s="5"/>
       <c r="K15" s="10"/>
       <c r="L15" s="11"/>
-      <c r="N15" s="20" t="s">
+      <c r="N15" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="O15" s="22">
-        <f>SUMIF(I7:I206, "zakat maal", J7:J206)</f>
+      <c r="O15" s="17">
+        <f>SUMIF(I6:I206, "zakat maal", J6:J206)</f>
         <v>0</v>
       </c>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="24"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="19"/>
     </row>
     <row r="16" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
@@ -924,12 +1374,12 @@
       <c r="J16" s="5"/>
       <c r="K16" s="10"/>
       <c r="L16" s="11"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="26"/>
-      <c r="Q16" s="26"/>
-      <c r="R16" s="26"/>
-      <c r="S16" s="27"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="22"/>
     </row>
     <row r="17" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
@@ -944,17 +1394,17 @@
       <c r="J17" s="5"/>
       <c r="K17" s="10"/>
       <c r="L17" s="11"/>
-      <c r="N17" s="12" t="s">
+      <c r="N17" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="O17" s="14">
-        <f>SUMIF(I7:I206, "infaq", J7:J206)</f>
+      <c r="O17" s="33">
+        <f>SUMIF(I6:I206, "infaq", J6:J206)</f>
         <v>0</v>
       </c>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="16"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
+      <c r="S17" s="35"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3"/>
@@ -969,12 +1419,12 @@
       <c r="J18" s="5"/>
       <c r="K18" s="10"/>
       <c r="L18" s="11"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="18"/>
-      <c r="R18" s="18"/>
-      <c r="S18" s="19"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="37"/>
+      <c r="R18" s="37"/>
+      <c r="S18" s="38"/>
     </row>
     <row r="19" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
@@ -989,17 +1439,17 @@
       <c r="J19" s="5"/>
       <c r="K19" s="10"/>
       <c r="L19" s="11"/>
-      <c r="N19" s="12" t="s">
+      <c r="N19" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="O19" s="14">
-        <f>SUMIF(I7:I206, "shodaqoh", J7:J206)</f>
+      <c r="O19" s="33">
+        <f>SUMIF(I6:I206, "shodaqoh", J6:J206)</f>
         <v>0</v>
       </c>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-      <c r="S19" s="16"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="35"/>
     </row>
     <row r="20" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
@@ -1014,12 +1464,12 @@
       <c r="J20" s="5"/>
       <c r="K20" s="10"/>
       <c r="L20" s="11"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="18"/>
-      <c r="R20" s="18"/>
-      <c r="S20" s="19"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="37"/>
+      <c r="R20" s="37"/>
+      <c r="S20" s="38"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
@@ -1034,17 +1484,17 @@
       <c r="J21" s="5"/>
       <c r="K21" s="10"/>
       <c r="L21" s="11"/>
-      <c r="N21" s="12" t="s">
+      <c r="N21" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="O21" s="14">
-        <f>SUM(J7:J206)</f>
+      <c r="O21" s="33">
+        <f>SUM(J6:J206)</f>
         <v>0</v>
       </c>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="16"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="35"/>
     </row>
     <row r="22" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
@@ -1059,12 +1509,12 @@
       <c r="J22" s="5"/>
       <c r="K22" s="10"/>
       <c r="L22" s="11"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="18"/>
-      <c r="Q22" s="18"/>
-      <c r="R22" s="18"/>
-      <c r="S22" s="19"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="37"/>
+      <c r="Q22" s="37"/>
+      <c r="R22" s="37"/>
+      <c r="S22" s="38"/>
     </row>
     <row r="23" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
@@ -6819,32 +7269,7 @@
       <c r="J1003" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J6" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="No"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <mergeCells count="26">
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="O15:S16"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="O13:S14"/>
-    <mergeCell ref="N9:S10"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="N15:N16"/>
+  <mergeCells count="16">
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="O19:S20"/>
     <mergeCell ref="N11:N12"/>
@@ -6853,8 +7278,19 @@
     <mergeCell ref="N21:N22"/>
     <mergeCell ref="O17:S18"/>
     <mergeCell ref="N17:N18"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O15:S16"/>
+    <mergeCell ref="O13:S14"/>
+    <mergeCell ref="N9:S10"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>